--- a/TestCasesForPrestaShop.xlsx
+++ b/TestCasesForPrestaShop.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\PrestaShop-Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5EB9FC-249B-43DF-98C4-11612FADFBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1432F0-1D74-44E2-A1C9-4B3C7A79DC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Module" sheetId="1" r:id="rId1"/>
     <sheet name="Registration" sheetId="2" r:id="rId2"/>
+    <sheet name="AddToCart" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="384">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -1055,6 +1056,251 @@
   </si>
   <si>
     <t>Data privacy box: Checked</t>
+  </si>
+  <si>
+    <t>TC012</t>
+  </si>
+  <si>
+    <t>TC013</t>
+  </si>
+  <si>
+    <t>User is on dashboard page</t>
+  </si>
+  <si>
+    <t>1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on Add to cart button</t>
+  </si>
+  <si>
+    <t>Verify that product is added multiple quantities</t>
+  </si>
+  <si>
+    <t>1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on Quantity increase arrow
+5]Click on Add to cart button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that product is added multiple quantities maximum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on Quantity increase arrow till 50 
+</t>
+  </si>
+  <si>
+    <t>User can add maximum quantity which present in stock</t>
+  </si>
+  <si>
+    <t>To verify that the price in the shopping cart is calculated correctly based on the unit price of the product multiplied by the selected quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on Quantity increase arrow 
+5]Click on add to cart
+</t>
+  </si>
+  <si>
+    <t>The total price displayed in  the cart should be equal to the unit price of the product multiplied by the selected quantity.The price should update automatically when the quantity is changed.</t>
+  </si>
+  <si>
+    <t>To verify that user can add multiple product quantities in single product</t>
+  </si>
+  <si>
+    <t>To verify product is accepts maximum quantities</t>
+  </si>
+  <si>
+    <t>Product quantity is accepting max 12 Quantities</t>
+  </si>
+  <si>
+    <t>Verify price calculation in cart is calculated correctly</t>
+  </si>
+  <si>
+    <t>Verify that product is added succesfully in cart</t>
+  </si>
+  <si>
+    <t>To verify that product is succesfully added in the cart after clicking add to cart button</t>
+  </si>
+  <si>
+    <t>Product should added succesfully in the cart and see alert message "product successfully added to your cart</t>
+  </si>
+  <si>
+    <t>Product succesfully added multiple quantities</t>
+  </si>
+  <si>
+    <t>To verify that a prodcut is added in that cart and then refreshing the page doest empty cart</t>
+  </si>
+  <si>
+    <t>1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on add to cart
+5]Click on back arrow
+6]Refresh the page</t>
+  </si>
+  <si>
+    <t>Refreshing page doest remove already added product in cart</t>
+  </si>
+  <si>
+    <t>Refreshing page remove all product in the cart</t>
+  </si>
+  <si>
+    <t>Verify that the product added to the cart matches the selected product details</t>
+  </si>
+  <si>
+    <t>To verify that product added to the cart is same product which is present in cart also</t>
+  </si>
+  <si>
+    <t>1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on "add to cart"
+5]Click on cart view
+6]Compare product details shown in the cart</t>
+  </si>
+  <si>
+    <t>The Product name ,price and quantity displayed in the cart should exactly matches the selected products details</t>
+  </si>
+  <si>
+    <t>Verify that Product price is dynamically changed with product quantities in cart</t>
+  </si>
+  <si>
+    <t>User is on  Shopping cart</t>
+  </si>
+  <si>
+    <t>To verify that product price is calculated correctly after changing its quantities or deleting product in cart</t>
+  </si>
+  <si>
+    <t>1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on "add to cart"
+5]Click on cart view
+6]User should see all products in cart
+7]User changed Quantities</t>
+  </si>
+  <si>
+    <t>The Product price is changing correctly after updating product quantities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that Product can succussfully removed from cart </t>
+  </si>
+  <si>
+    <t>1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on "add to cart"
+5]Click on cart view
+6]User should see all products in cart
+7]User Click on delete button on any product</t>
+  </si>
+  <si>
+    <t>The Product is succsfully remove from cart</t>
+  </si>
+  <si>
+    <t>To verify that product quantity can increase or descrease through manually</t>
+  </si>
+  <si>
+    <t>Verify that manually update the quantity of product in cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on "add to cart"
+5]Click on cart view
+6]User should see all products in cart
+7]User manually updating product quantity
+</t>
+  </si>
+  <si>
+    <t>The Product quantity quantity updating manually</t>
+  </si>
+  <si>
+    <t>Verify that already added product in cart doesn't remove after refreshingpage</t>
+  </si>
+  <si>
+    <t>To verify that product is successfullyremove from cart after clicking delete view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that after session end cart product is removed </t>
+  </si>
+  <si>
+    <t>To verify that after Logout and login again cart retained or cleared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on "add to cart"
+5]Click on cart view
+6]User should see all products in cart
+7]User click on  Signout button
+8]User click sign in again with same credential
+</t>
+  </si>
+  <si>
+    <t>The product should retained after logout and login again</t>
+  </si>
+  <si>
+    <t>The product clear from cart after logout and login again</t>
+  </si>
+  <si>
+    <t>Verify that you cannot add special characters in quantity manually</t>
+  </si>
+  <si>
+    <t>To verify that special character cannot be added in the quantity  section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1]User should present in dashboard
+2]User click on Product
+3]User should see product information in page
+4]Click on "add to cart"
+5]Click on cart view
+6]User should see all products in cart
+7]User click on  quantity Section
+8]User add special character insted integer
+</t>
+  </si>
+  <si>
+    <t>System cannot add any special character or negative number in quantity section</t>
+  </si>
+  <si>
+    <t>Verify that after adding more than 50 products in cart will affect UI and stability</t>
+  </si>
+  <si>
+    <t>To verify that after adding more than 50 products Ui responsive and stability will not hamper</t>
+  </si>
+  <si>
+    <t>1]User should present in dashboard
+2]User click on more than 50 Products
+3]User should see product information in page
+4]Click on "add to cart"
+5]Click on cart view
+6]User should see all products in cart
+7]Click back on dashboard</t>
+  </si>
+  <si>
+    <t>System cannot slow after adding more than 50 products in the cart at one time</t>
+  </si>
+  <si>
+    <t>Verify that this website is compatible for all devices with mobile and small devices</t>
+  </si>
+  <si>
+    <t>To verify that website are compatible for all devices with small and high resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1] The user open website in all devices like mobile,tablets,with high resolution
+</t>
+  </si>
+  <si>
+    <t>The website will work comfortablity with all devices</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1248,48 +1494,35 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1839,7 +2072,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
@@ -1868,7 +2101,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>34</v>
       </c>
@@ -2244,7 +2477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>86</v>
       </c>
@@ -2302,7 +2535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>88</v>
       </c>
@@ -2577,7 +2810,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>197</v>
       </c>
       <c r="B20" s="18"/>
@@ -2672,7 +2905,7 @@
       <c r="H23" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="I23" s="24" t="s">
+      <c r="I23" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2680,13 +2913,13 @@
       <c r="A24" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="10" t="s">
         <v>258</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="10" t="s">
         <v>259</v>
       </c>
       <c r="E24" s="10" t="s">
@@ -2701,7 +2934,7 @@
       <c r="H24" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="I24" s="24" t="s">
+      <c r="I24" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2709,13 +2942,13 @@
       <c r="A25" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="10" t="s">
         <v>210</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="10" t="s">
         <v>260</v>
       </c>
       <c r="E25" s="10" t="s">
@@ -2738,13 +2971,13 @@
       <c r="A26" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="10" t="s">
         <v>222</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="10" t="s">
         <v>214</v>
       </c>
       <c r="E26" s="10" t="s">
@@ -2767,13 +3000,13 @@
       <c r="A27" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="10" t="s">
         <v>261</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="10" t="s">
         <v>217</v>
       </c>
       <c r="E27" s="10" t="s">
@@ -2782,10 +3015,10 @@
       <c r="F27" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="10" t="s">
         <v>220</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -2793,35 +3026,35 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="29"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="19"/>
       <c r="E28" s="19"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="26"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="10" t="s">
         <v>224</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="10" t="s">
         <v>225</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="10" t="s">
         <v>227</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -2830,7 +3063,7 @@
       <c r="H29" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I29" s="30" t="s">
+      <c r="I29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2838,26 +3071,26 @@
       <c r="A30" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="10" t="s">
         <v>228</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="10" t="s">
         <v>229</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>230</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="24" t="s">
+      <c r="G30" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="H30" s="24" t="s">
+      <c r="H30" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="I30" s="30" t="s">
+      <c r="I30" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2865,13 +3098,13 @@
       <c r="A31" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="10" t="s">
         <v>232</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="10" t="s">
         <v>233</v>
       </c>
       <c r="E31" s="10" t="s">
@@ -2884,7 +3117,7 @@
       <c r="H31" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I31" s="30" t="s">
+      <c r="I31" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2892,13 +3125,13 @@
       <c r="A32" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="10" t="s">
         <v>235</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="10" t="s">
         <v>239</v>
       </c>
       <c r="E32" s="10" t="s">
@@ -2911,7 +3144,7 @@
       <c r="H32" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I32" s="30" t="s">
+      <c r="I32" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2919,13 +3152,13 @@
       <c r="A33" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="10" t="s">
         <v>237</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="10" t="s">
         <v>240</v>
       </c>
       <c r="E33" s="10" t="s">
@@ -2938,7 +3171,7 @@
       <c r="H33" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="I33" s="30" t="s">
+      <c r="I33" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2946,13 +3179,13 @@
       <c r="A34" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="10" t="s">
         <v>238</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="10" t="s">
         <v>241</v>
       </c>
       <c r="E34" s="10" t="s">
@@ -2965,7 +3198,7 @@
       <c r="H34" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="I34" s="30" t="s">
+      <c r="I34" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2973,13 +3206,13 @@
       <c r="A35" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="10" t="s">
         <v>236</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="10" t="s">
         <v>242</v>
       </c>
       <c r="E35" s="10" t="s">
@@ -2992,7 +3225,7 @@
       <c r="H35" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I35" s="30" t="s">
+      <c r="I35" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3000,41 +3233,40 @@
       <c r="A36" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="28"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="10" t="s">
         <v>245</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="10" t="s">
         <v>246</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="G37" s="30" t="s">
+      <c r="G37" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H37" s="30" t="s">
+      <c r="H37" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I37" s="30" t="s">
+      <c r="I37" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3042,28 +3274,28 @@
       <c r="A38" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="10" t="s">
         <v>249</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="10" t="s">
         <v>252</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="G38" s="30" t="s">
+      <c r="G38" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="H38" s="30" t="s">
+      <c r="H38" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="I38" s="30" t="s">
+      <c r="I38" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3071,19 +3303,19 @@
       <c r="A39" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="10" t="s">
         <v>254</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="10" t="s">
         <v>255</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="10" t="s">
         <v>253</v>
       </c>
       <c r="G39" s="6" t="s">
@@ -3092,7 +3324,7 @@
       <c r="H39" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I39" s="30" t="s">
+      <c r="I39" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3100,22 +3332,22 @@
       <c r="A40" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="10" t="s">
         <v>267</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="10" t="s">
         <v>268</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="G40" s="30" t="s">
+      <c r="G40" s="6" t="s">
         <v>263</v>
       </c>
       <c r="H40" s="6" t="s">
@@ -3129,473 +3361,521 @@
       <c r="A41" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="10" t="s">
         <v>266</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="10" t="s">
         <v>269</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F41" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="G41" s="30" t="s">
+      <c r="G41" s="6" t="s">
         <v>265</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="I41" s="34" t="s">
+      <c r="I41" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="33"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="25"/>
     </row>
     <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="35" t="s">
+      <c r="A43" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C43" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="35" t="s">
+      <c r="D43" s="28" t="s">
         <v>281</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="F43" s="35" t="s">
+      <c r="F43" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="G43" s="35" t="s">
+      <c r="G43" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="H43" s="35" t="s">
+      <c r="H43" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="I43" s="35" t="s">
+      <c r="I43" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="35"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="35"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
       <c r="E45" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
     </row>
     <row r="46" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="C46" s="35" t="s">
+      <c r="C46" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="28" t="s">
         <v>287</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="G46" s="35" t="s">
+      <c r="G46" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="H46" s="35" t="s">
+      <c r="H46" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="I46" s="35" t="s">
+      <c r="I46" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="35"/>
-      <c r="B47" s="35"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="35"/>
-      <c r="B48" s="35"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
       <c r="E48" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
     </row>
     <row r="49" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="B49" s="35" t="s">
+      <c r="B49" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="C49" s="35" t="s">
+      <c r="C49" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="35" t="s">
+      <c r="D49" s="28" t="s">
         <v>295</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="F49" s="35" t="s">
+      <c r="F49" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="G49" s="35" t="s">
+      <c r="G49" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="H49" s="35" t="s">
+      <c r="H49" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="I49" s="35" t="s">
+      <c r="I49" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="35"/>
-      <c r="B50" s="35"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
       <c r="E50" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="35"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
       <c r="E51" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="35"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
     </row>
     <row r="52" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="35" t="s">
+      <c r="A52" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="C52" s="35" t="s">
+      <c r="C52" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="35" t="s">
+      <c r="D52" s="28" t="s">
         <v>302</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="G52" s="35" t="s">
+      <c r="G52" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="H52" s="35" t="s">
+      <c r="H52" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="I52" s="35" t="s">
+      <c r="I52" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="35"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
       <c r="E53" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="35"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
       <c r="E54" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
     </row>
     <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="35" t="s">
+      <c r="A55" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="B55" s="35" t="s">
+      <c r="B55" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="C55" s="35" t="s">
+      <c r="C55" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D55" s="35" t="s">
+      <c r="D55" s="28" t="s">
         <v>308</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F55" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="G55" s="35" t="s">
+      <c r="G55" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="H55" s="35" t="s">
+      <c r="H55" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="I55" s="35" t="s">
+      <c r="I55" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="35"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
+      <c r="A56" s="28"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
       <c r="E56" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="35"/>
-      <c r="B57" s="35"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
       <c r="E57" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
     </row>
     <row r="58" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="35" t="s">
+      <c r="A58" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="C58" s="35" t="s">
+      <c r="C58" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="28" t="s">
         <v>312</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="F58" s="35" t="s">
+      <c r="F58" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="G58" s="35" t="s">
+      <c r="G58" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="H58" s="35" t="s">
+      <c r="H58" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="I58" s="35" t="s">
+      <c r="I58" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="35"/>
-      <c r="B59" s="35"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
       <c r="E59" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
     </row>
     <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="35" t="s">
+      <c r="A60" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="C60" s="35" t="s">
+      <c r="C60" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D60" s="35" t="s">
+      <c r="D60" s="28" t="s">
         <v>317</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="F60" s="35" t="s">
+      <c r="F60" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="G60" s="35" t="s">
+      <c r="G60" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="H60" s="35" t="s">
+      <c r="H60" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="I60" s="35" t="s">
+      <c r="I60" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="35"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
       <c r="E61" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="35"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
+      <c r="A62" s="28"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
       <c r="E62" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
     </row>
     <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="B63" s="35" t="s">
+      <c r="B63" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="C63" s="35" t="s">
+      <c r="C63" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D63" s="35" t="s">
+      <c r="D63" s="28" t="s">
         <v>322</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="F63" s="35" t="s">
+      <c r="F63" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="G63" s="35" t="s">
+      <c r="G63" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="H63" s="35" t="s">
+      <c r="H63" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="I63" s="35" t="s">
+      <c r="I63" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="35"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
       <c r="E64" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="35"/>
-      <c r="B65" s="35"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
+      <c r="A65" s="28"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
       <c r="E65" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="H43:H45"/>
+    <mergeCell ref="I43:I45"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="I46:I48"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="H49:H51"/>
+    <mergeCell ref="I49:I51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="H52:H54"/>
+    <mergeCell ref="I52:I54"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="F55:F57"/>
+    <mergeCell ref="G55:G57"/>
     <mergeCell ref="H60:H62"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="A63:A65"/>
@@ -3612,56 +3892,473 @@
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="G60:G62"/>
-    <mergeCell ref="H55:H57"/>
-    <mergeCell ref="I55:I57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="F55:F57"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="I49:I51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="H43:H45"/>
-    <mergeCell ref="I43:I45"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="I46:I48"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A58655-BAD3-4B5E-BDA1-4FCA7B51CC69}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" style="27" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" style="27" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="22" style="27" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="20" style="27" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="27" customWidth="1"/>
+    <col min="9" max="9" width="23.77734375" style="27" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="141.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="127.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="143.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="216" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="216" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>